--- a/raw/Timetable_2026Autumn_2025IE.xlsx
+++ b/raw/Timetable_2026Autumn_2025IE.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BD1E08B-32D0-49FF-9FCB-823B393C1849}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B3D9550-3994-4998-8BD7-B044ADE6D2FB}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="181">
   <si>
     <t>week</t>
   </si>
@@ -1072,43 +1072,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1135,6 +1099,42 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1144,15 +1144,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1160,21 +1151,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1187,6 +1163,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1536,78 +1536,78 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="76" t="s">
+      <c r="C2" s="64"/>
+      <c r="D2" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="77"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="76" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="76" t="s">
+      <c r="H2" s="78"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="77"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="76" t="s">
+      <c r="K2" s="78"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="77"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="76" t="s">
+      <c r="N2" s="78"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="76" t="s">
+      <c r="Q2" s="78"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="77"/>
-      <c r="U2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="79"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="76" t="s">
+      <c r="A3" s="83"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="77"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="76" t="s">
+      <c r="E3" s="78"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="77"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="76" t="s">
+      <c r="H3" s="78"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="77"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="76" t="s">
+      <c r="K3" s="78"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="77"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="76" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="76" t="s">
+      <c r="Q3" s="78"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="77"/>
-      <c r="U3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="79"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="67">
@@ -1970,7 +1970,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="73">
+      <c r="A11" s="70">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -2036,7 +2036,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="74"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="13" t="s">
         <v>47</v>
       </c>
@@ -2098,7 +2098,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="74"/>
+      <c r="A13" s="71"/>
       <c r="B13" s="13" t="s">
         <v>49</v>
       </c>
@@ -2150,7 +2150,7 @@
       <c r="AA13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="74"/>
+      <c r="A14" s="71"/>
       <c r="B14" s="13" t="s">
         <v>50</v>
       </c>
@@ -2214,7 +2214,7 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="74"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="13" t="s">
         <v>54</v>
       </c>
@@ -2266,7 +2266,7 @@
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="74"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="13" t="s">
         <v>55</v>
       </c>
@@ -2293,7 +2293,7 @@
       <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="75"/>
+      <c r="A17" s="72"/>
       <c r="B17" s="13" t="s">
         <v>56</v>
       </c>
@@ -2623,7 +2623,7 @@
       <c r="U24" s="22"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="73">
+      <c r="A25" s="70">
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -2672,7 +2672,7 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="74"/>
+      <c r="A26" s="71"/>
       <c r="B26" s="13" t="s">
         <v>65</v>
       </c>
@@ -2719,7 +2719,7 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="74"/>
+      <c r="A27" s="71"/>
       <c r="B27" s="13" t="s">
         <v>66</v>
       </c>
@@ -2766,7 +2766,7 @@
       <c r="U27" s="17"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="74"/>
+      <c r="A28" s="71"/>
       <c r="B28" s="13" t="s">
         <v>67</v>
       </c>
@@ -2813,87 +2813,87 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="74"/>
+      <c r="A29" s="71"/>
       <c r="B29" s="25" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="49"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="58"/>
+      <c r="R29" s="58"/>
+      <c r="S29" s="58"/>
+      <c r="T29" s="58"/>
+      <c r="U29" s="59"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="74"/>
+      <c r="A30" s="71"/>
       <c r="B30" s="25" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="71"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="48"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="49"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="58"/>
+      <c r="R30" s="58"/>
+      <c r="S30" s="58"/>
+      <c r="T30" s="58"/>
+      <c r="U30" s="59"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="75"/>
+      <c r="A31" s="72"/>
       <c r="B31" s="25" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="72"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="51"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="67">
@@ -3046,26 +3046,26 @@
       <c r="C35" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="70" t="s">
+      <c r="D35" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="46"/>
-      <c r="P35" s="46"/>
-      <c r="Q35" s="46"/>
-      <c r="R35" s="46"/>
-      <c r="S35" s="46"/>
-      <c r="T35" s="46"/>
-      <c r="U35" s="47"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="56"/>
+      <c r="O35" s="56"/>
+      <c r="P35" s="56"/>
+      <c r="Q35" s="56"/>
+      <c r="R35" s="56"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="56"/>
+      <c r="U35" s="57"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A36" s="68"/>
@@ -3075,24 +3075,24 @@
       <c r="C36" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="71"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="48"/>
-      <c r="N36" s="48"/>
-      <c r="O36" s="48"/>
-      <c r="P36" s="48"/>
-      <c r="Q36" s="48"/>
-      <c r="R36" s="48"/>
-      <c r="S36" s="48"/>
-      <c r="T36" s="48"/>
-      <c r="U36" s="49"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="58"/>
+      <c r="L36" s="58"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="58"/>
+      <c r="O36" s="58"/>
+      <c r="P36" s="58"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="58"/>
+      <c r="S36" s="58"/>
+      <c r="T36" s="58"/>
+      <c r="U36" s="59"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="68"/>
@@ -3102,24 +3102,24 @@
       <c r="C37" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="71"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
-      <c r="L37" s="48"/>
-      <c r="M37" s="48"/>
-      <c r="N37" s="48"/>
-      <c r="O37" s="48"/>
-      <c r="P37" s="48"/>
-      <c r="Q37" s="48"/>
-      <c r="R37" s="48"/>
-      <c r="S37" s="48"/>
-      <c r="T37" s="48"/>
-      <c r="U37" s="49"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="58"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="58"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="58"/>
+      <c r="Q37" s="58"/>
+      <c r="R37" s="58"/>
+      <c r="S37" s="58"/>
+      <c r="T37" s="58"/>
+      <c r="U37" s="59"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A38" s="69"/>
@@ -3129,27 +3129,27 @@
       <c r="C38" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="71"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="48"/>
-      <c r="L38" s="48"/>
-      <c r="M38" s="48"/>
-      <c r="N38" s="48"/>
-      <c r="O38" s="48"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="48"/>
-      <c r="R38" s="48"/>
-      <c r="S38" s="48"/>
-      <c r="T38" s="48"/>
-      <c r="U38" s="49"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="58"/>
+      <c r="S38" s="58"/>
+      <c r="T38" s="58"/>
+      <c r="U38" s="59"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="73">
+      <c r="A39" s="70">
         <v>6</v>
       </c>
       <c r="B39" s="27" t="s">
@@ -3158,81 +3158,81 @@
       <c r="C39" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="71"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
-      <c r="L39" s="48"/>
-      <c r="M39" s="48"/>
-      <c r="N39" s="48"/>
-      <c r="O39" s="48"/>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="48"/>
-      <c r="R39" s="48"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="48"/>
-      <c r="U39" s="49"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="58"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
+      <c r="P39" s="58"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="58"/>
+      <c r="S39" s="58"/>
+      <c r="T39" s="58"/>
+      <c r="U39" s="59"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="74"/>
+      <c r="A40" s="71"/>
       <c r="B40" s="27" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="71"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
-      <c r="L40" s="48"/>
-      <c r="M40" s="48"/>
-      <c r="N40" s="48"/>
-      <c r="O40" s="48"/>
-      <c r="P40" s="48"/>
-      <c r="Q40" s="48"/>
-      <c r="R40" s="48"/>
-      <c r="S40" s="48"/>
-      <c r="T40" s="48"/>
-      <c r="U40" s="49"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="58"/>
+      <c r="Q40" s="58"/>
+      <c r="R40" s="58"/>
+      <c r="S40" s="58"/>
+      <c r="T40" s="58"/>
+      <c r="U40" s="59"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="74"/>
+      <c r="A41" s="71"/>
       <c r="B41" s="27" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="72"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
-      <c r="O41" s="50"/>
-      <c r="P41" s="50"/>
-      <c r="Q41" s="50"/>
-      <c r="R41" s="50"/>
-      <c r="S41" s="50"/>
-      <c r="T41" s="50"/>
-      <c r="U41" s="51"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="61"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="74"/>
+      <c r="A42" s="71"/>
       <c r="B42" s="28" t="s">
         <v>82</v>
       </c>
@@ -3291,7 +3291,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="74"/>
+      <c r="A43" s="71"/>
       <c r="B43" s="28" t="s">
         <v>83</v>
       </c>
@@ -3320,7 +3320,7 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="74"/>
+      <c r="A44" s="71"/>
       <c r="B44" s="29" t="s">
         <v>84</v>
       </c>
@@ -3347,7 +3347,7 @@
       <c r="U44" s="22"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="75"/>
+      <c r="A45" s="72"/>
       <c r="B45" s="28" t="s">
         <v>85</v>
       </c>
@@ -3665,7 +3665,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="73">
+      <c r="A53" s="70">
         <v>8</v>
       </c>
       <c r="B53" s="28" t="s">
@@ -3714,7 +3714,7 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="74"/>
+      <c r="A54" s="71"/>
       <c r="B54" s="28" t="s">
         <v>94</v>
       </c>
@@ -3761,7 +3761,7 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="74"/>
+      <c r="A55" s="71"/>
       <c r="B55" s="28" t="s">
         <v>95</v>
       </c>
@@ -3808,7 +3808,7 @@
       <c r="U55" s="17"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="74"/>
+      <c r="A56" s="71"/>
       <c r="B56" s="28" t="s">
         <v>96</v>
       </c>
@@ -3867,7 +3867,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="74"/>
+      <c r="A57" s="71"/>
       <c r="B57" s="28" t="s">
         <v>97</v>
       </c>
@@ -3914,7 +3914,7 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="74"/>
+      <c r="A58" s="71"/>
       <c r="B58" s="28" t="s">
         <v>98</v>
       </c>
@@ -3941,7 +3941,7 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="75"/>
+      <c r="A59" s="72"/>
       <c r="B59" s="28" t="s">
         <v>99</v>
       </c>
@@ -4235,7 +4235,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="73">
+      <c r="A67" s="70">
         <v>10</v>
       </c>
       <c r="B67" s="28" t="s">
@@ -4284,7 +4284,7 @@
       <c r="U67" s="16"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="74"/>
+      <c r="A68" s="71"/>
       <c r="B68" s="28" t="s">
         <v>108</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="U68" s="16"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="74"/>
+      <c r="A69" s="71"/>
       <c r="B69" s="28" t="s">
         <v>109</v>
       </c>
@@ -4342,7 +4342,7 @@
       <c r="U69" s="16"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="74"/>
+      <c r="A70" s="71"/>
       <c r="B70" s="28" t="s">
         <v>110</v>
       </c>
@@ -4401,7 +4401,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="74"/>
+      <c r="A71" s="71"/>
       <c r="B71" s="28" t="s">
         <v>111</v>
       </c>
@@ -4430,7 +4430,7 @@
       <c r="U71" s="16"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="74"/>
+      <c r="A72" s="71"/>
       <c r="B72" s="28" t="s">
         <v>112</v>
       </c>
@@ -4457,7 +4457,7 @@
       <c r="U72" s="16"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="75"/>
+      <c r="A73" s="72"/>
       <c r="B73" s="28" t="s">
         <v>113</v>
       </c>
@@ -4721,7 +4721,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="73">
+      <c r="A81" s="70">
         <v>12</v>
       </c>
       <c r="B81" s="28" t="s">
@@ -4730,188 +4730,188 @@
       <c r="C81" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="82" t="s">
+      <c r="D81" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="E81" s="61"/>
-      <c r="F81" s="61"/>
-      <c r="G81" s="61"/>
-      <c r="H81" s="61"/>
-      <c r="I81" s="61"/>
-      <c r="J81" s="61"/>
-      <c r="K81" s="61"/>
-      <c r="L81" s="61"/>
-      <c r="M81" s="61"/>
-      <c r="N81" s="61"/>
-      <c r="O81" s="61"/>
-      <c r="P81" s="61"/>
-      <c r="Q81" s="61"/>
-      <c r="R81" s="61"/>
-      <c r="S81" s="61"/>
-      <c r="T81" s="61"/>
-      <c r="U81" s="62"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="49"/>
+      <c r="H81" s="49"/>
+      <c r="I81" s="49"/>
+      <c r="J81" s="49"/>
+      <c r="K81" s="49"/>
+      <c r="L81" s="49"/>
+      <c r="M81" s="49"/>
+      <c r="N81" s="49"/>
+      <c r="O81" s="49"/>
+      <c r="P81" s="49"/>
+      <c r="Q81" s="49"/>
+      <c r="R81" s="49"/>
+      <c r="S81" s="49"/>
+      <c r="T81" s="49"/>
+      <c r="U81" s="50"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="74"/>
+      <c r="A82" s="71"/>
       <c r="B82" s="28" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="83"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="63"/>
-      <c r="G82" s="63"/>
-      <c r="H82" s="63"/>
-      <c r="I82" s="63"/>
-      <c r="J82" s="63"/>
-      <c r="K82" s="63"/>
-      <c r="L82" s="63"/>
-      <c r="M82" s="63"/>
-      <c r="N82" s="63"/>
-      <c r="O82" s="63"/>
-      <c r="P82" s="63"/>
-      <c r="Q82" s="63"/>
-      <c r="R82" s="63"/>
-      <c r="S82" s="63"/>
-      <c r="T82" s="63"/>
-      <c r="U82" s="64"/>
+      <c r="D82" s="75"/>
+      <c r="E82" s="51"/>
+      <c r="F82" s="51"/>
+      <c r="G82" s="51"/>
+      <c r="H82" s="51"/>
+      <c r="I82" s="51"/>
+      <c r="J82" s="51"/>
+      <c r="K82" s="51"/>
+      <c r="L82" s="51"/>
+      <c r="M82" s="51"/>
+      <c r="N82" s="51"/>
+      <c r="O82" s="51"/>
+      <c r="P82" s="51"/>
+      <c r="Q82" s="51"/>
+      <c r="R82" s="51"/>
+      <c r="S82" s="51"/>
+      <c r="T82" s="51"/>
+      <c r="U82" s="52"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="74"/>
+      <c r="A83" s="71"/>
       <c r="B83" s="28" t="s">
         <v>124</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D83" s="83"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="63"/>
-      <c r="I83" s="63"/>
-      <c r="J83" s="63"/>
-      <c r="K83" s="63"/>
-      <c r="L83" s="63"/>
-      <c r="M83" s="63"/>
-      <c r="N83" s="63"/>
-      <c r="O83" s="63"/>
-      <c r="P83" s="63"/>
-      <c r="Q83" s="63"/>
-      <c r="R83" s="63"/>
-      <c r="S83" s="63"/>
-      <c r="T83" s="63"/>
-      <c r="U83" s="64"/>
+      <c r="D83" s="75"/>
+      <c r="E83" s="51"/>
+      <c r="F83" s="51"/>
+      <c r="G83" s="51"/>
+      <c r="H83" s="51"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="51"/>
+      <c r="K83" s="51"/>
+      <c r="L83" s="51"/>
+      <c r="M83" s="51"/>
+      <c r="N83" s="51"/>
+      <c r="O83" s="51"/>
+      <c r="P83" s="51"/>
+      <c r="Q83" s="51"/>
+      <c r="R83" s="51"/>
+      <c r="S83" s="51"/>
+      <c r="T83" s="51"/>
+      <c r="U83" s="52"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="74"/>
+      <c r="A84" s="71"/>
       <c r="B84" s="28" t="s">
         <v>125</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D84" s="83"/>
-      <c r="E84" s="63"/>
-      <c r="F84" s="63"/>
-      <c r="G84" s="63"/>
-      <c r="H84" s="63"/>
-      <c r="I84" s="63"/>
-      <c r="J84" s="63"/>
-      <c r="K84" s="63"/>
-      <c r="L84" s="63"/>
-      <c r="M84" s="63"/>
-      <c r="N84" s="63"/>
-      <c r="O84" s="63"/>
-      <c r="P84" s="63"/>
-      <c r="Q84" s="63"/>
-      <c r="R84" s="63"/>
-      <c r="S84" s="63"/>
-      <c r="T84" s="63"/>
-      <c r="U84" s="64"/>
+      <c r="D84" s="75"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="51"/>
+      <c r="I84" s="51"/>
+      <c r="J84" s="51"/>
+      <c r="K84" s="51"/>
+      <c r="L84" s="51"/>
+      <c r="M84" s="51"/>
+      <c r="N84" s="51"/>
+      <c r="O84" s="51"/>
+      <c r="P84" s="51"/>
+      <c r="Q84" s="51"/>
+      <c r="R84" s="51"/>
+      <c r="S84" s="51"/>
+      <c r="T84" s="51"/>
+      <c r="U84" s="52"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="74"/>
+      <c r="A85" s="71"/>
       <c r="B85" s="28" t="s">
         <v>126</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D85" s="83"/>
-      <c r="E85" s="63"/>
-      <c r="F85" s="63"/>
-      <c r="G85" s="63"/>
-      <c r="H85" s="63"/>
-      <c r="I85" s="63"/>
-      <c r="J85" s="63"/>
-      <c r="K85" s="63"/>
-      <c r="L85" s="63"/>
-      <c r="M85" s="63"/>
-      <c r="N85" s="63"/>
-      <c r="O85" s="63"/>
-      <c r="P85" s="63"/>
-      <c r="Q85" s="63"/>
-      <c r="R85" s="63"/>
-      <c r="S85" s="63"/>
-      <c r="T85" s="63"/>
-      <c r="U85" s="64"/>
+      <c r="D85" s="75"/>
+      <c r="E85" s="51"/>
+      <c r="F85" s="51"/>
+      <c r="G85" s="51"/>
+      <c r="H85" s="51"/>
+      <c r="I85" s="51"/>
+      <c r="J85" s="51"/>
+      <c r="K85" s="51"/>
+      <c r="L85" s="51"/>
+      <c r="M85" s="51"/>
+      <c r="N85" s="51"/>
+      <c r="O85" s="51"/>
+      <c r="P85" s="51"/>
+      <c r="Q85" s="51"/>
+      <c r="R85" s="51"/>
+      <c r="S85" s="51"/>
+      <c r="T85" s="51"/>
+      <c r="U85" s="52"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="74"/>
+      <c r="A86" s="71"/>
       <c r="B86" s="28" t="s">
         <v>127</v>
       </c>
       <c r="C86" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="83"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="63"/>
-      <c r="G86" s="63"/>
-      <c r="H86" s="63"/>
-      <c r="I86" s="63"/>
-      <c r="J86" s="63"/>
-      <c r="K86" s="63"/>
-      <c r="L86" s="63"/>
-      <c r="M86" s="63"/>
-      <c r="N86" s="63"/>
-      <c r="O86" s="63"/>
-      <c r="P86" s="63"/>
-      <c r="Q86" s="63"/>
-      <c r="R86" s="63"/>
-      <c r="S86" s="63"/>
-      <c r="T86" s="63"/>
-      <c r="U86" s="64"/>
+      <c r="D86" s="75"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="51"/>
+      <c r="G86" s="51"/>
+      <c r="H86" s="51"/>
+      <c r="I86" s="51"/>
+      <c r="J86" s="51"/>
+      <c r="K86" s="51"/>
+      <c r="L86" s="51"/>
+      <c r="M86" s="51"/>
+      <c r="N86" s="51"/>
+      <c r="O86" s="51"/>
+      <c r="P86" s="51"/>
+      <c r="Q86" s="51"/>
+      <c r="R86" s="51"/>
+      <c r="S86" s="51"/>
+      <c r="T86" s="51"/>
+      <c r="U86" s="52"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="75"/>
+      <c r="A87" s="72"/>
       <c r="B87" s="28" t="s">
         <v>128</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D87" s="83"/>
-      <c r="E87" s="63"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="63"/>
-      <c r="H87" s="63"/>
-      <c r="I87" s="63"/>
-      <c r="J87" s="63"/>
-      <c r="K87" s="63"/>
-      <c r="L87" s="63"/>
-      <c r="M87" s="63"/>
-      <c r="N87" s="63"/>
-      <c r="O87" s="63"/>
-      <c r="P87" s="63"/>
-      <c r="Q87" s="63"/>
-      <c r="R87" s="63"/>
-      <c r="S87" s="63"/>
-      <c r="T87" s="63"/>
-      <c r="U87" s="64"/>
+      <c r="D87" s="75"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="51"/>
+      <c r="J87" s="51"/>
+      <c r="K87" s="51"/>
+      <c r="L87" s="51"/>
+      <c r="M87" s="51"/>
+      <c r="N87" s="51"/>
+      <c r="O87" s="51"/>
+      <c r="P87" s="51"/>
+      <c r="Q87" s="51"/>
+      <c r="R87" s="51"/>
+      <c r="S87" s="51"/>
+      <c r="T87" s="51"/>
+      <c r="U87" s="52"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A88" s="67">
@@ -4923,24 +4923,24 @@
       <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="83"/>
-      <c r="E88" s="63"/>
-      <c r="F88" s="63"/>
-      <c r="G88" s="63"/>
-      <c r="H88" s="63"/>
-      <c r="I88" s="63"/>
-      <c r="J88" s="63"/>
-      <c r="K88" s="63"/>
-      <c r="L88" s="63"/>
-      <c r="M88" s="63"/>
-      <c r="N88" s="63"/>
-      <c r="O88" s="63"/>
-      <c r="P88" s="63"/>
-      <c r="Q88" s="63"/>
-      <c r="R88" s="63"/>
-      <c r="S88" s="63"/>
-      <c r="T88" s="63"/>
-      <c r="U88" s="64"/>
+      <c r="D88" s="75"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="51"/>
+      <c r="J88" s="51"/>
+      <c r="K88" s="51"/>
+      <c r="L88" s="51"/>
+      <c r="M88" s="51"/>
+      <c r="N88" s="51"/>
+      <c r="O88" s="51"/>
+      <c r="P88" s="51"/>
+      <c r="Q88" s="51"/>
+      <c r="R88" s="51"/>
+      <c r="S88" s="51"/>
+      <c r="T88" s="51"/>
+      <c r="U88" s="52"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="68"/>
@@ -4950,24 +4950,24 @@
       <c r="C89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="83"/>
-      <c r="E89" s="63"/>
-      <c r="F89" s="63"/>
-      <c r="G89" s="63"/>
-      <c r="H89" s="63"/>
-      <c r="I89" s="63"/>
-      <c r="J89" s="63"/>
-      <c r="K89" s="63"/>
-      <c r="L89" s="63"/>
-      <c r="M89" s="63"/>
-      <c r="N89" s="63"/>
-      <c r="O89" s="63"/>
-      <c r="P89" s="63"/>
-      <c r="Q89" s="63"/>
-      <c r="R89" s="63"/>
-      <c r="S89" s="63"/>
-      <c r="T89" s="63"/>
-      <c r="U89" s="64"/>
+      <c r="D89" s="75"/>
+      <c r="E89" s="51"/>
+      <c r="F89" s="51"/>
+      <c r="G89" s="51"/>
+      <c r="H89" s="51"/>
+      <c r="I89" s="51"/>
+      <c r="J89" s="51"/>
+      <c r="K89" s="51"/>
+      <c r="L89" s="51"/>
+      <c r="M89" s="51"/>
+      <c r="N89" s="51"/>
+      <c r="O89" s="51"/>
+      <c r="P89" s="51"/>
+      <c r="Q89" s="51"/>
+      <c r="R89" s="51"/>
+      <c r="S89" s="51"/>
+      <c r="T89" s="51"/>
+      <c r="U89" s="52"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A90" s="68"/>
@@ -4977,24 +4977,24 @@
       <c r="C90" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D90" s="83"/>
-      <c r="E90" s="63"/>
-      <c r="F90" s="63"/>
-      <c r="G90" s="63"/>
-      <c r="H90" s="63"/>
-      <c r="I90" s="63"/>
-      <c r="J90" s="63"/>
-      <c r="K90" s="63"/>
-      <c r="L90" s="63"/>
-      <c r="M90" s="63"/>
-      <c r="N90" s="63"/>
-      <c r="O90" s="63"/>
-      <c r="P90" s="63"/>
-      <c r="Q90" s="63"/>
-      <c r="R90" s="63"/>
-      <c r="S90" s="63"/>
-      <c r="T90" s="63"/>
-      <c r="U90" s="64"/>
+      <c r="D90" s="75"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="51"/>
+      <c r="G90" s="51"/>
+      <c r="H90" s="51"/>
+      <c r="I90" s="51"/>
+      <c r="J90" s="51"/>
+      <c r="K90" s="51"/>
+      <c r="L90" s="51"/>
+      <c r="M90" s="51"/>
+      <c r="N90" s="51"/>
+      <c r="O90" s="51"/>
+      <c r="P90" s="51"/>
+      <c r="Q90" s="51"/>
+      <c r="R90" s="51"/>
+      <c r="S90" s="51"/>
+      <c r="T90" s="51"/>
+      <c r="U90" s="52"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="68"/>
@@ -5004,24 +5004,24 @@
       <c r="C91" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D91" s="83"/>
-      <c r="E91" s="63"/>
-      <c r="F91" s="63"/>
-      <c r="G91" s="63"/>
-      <c r="H91" s="63"/>
-      <c r="I91" s="63"/>
-      <c r="J91" s="63"/>
-      <c r="K91" s="63"/>
-      <c r="L91" s="63"/>
-      <c r="M91" s="63"/>
-      <c r="N91" s="63"/>
-      <c r="O91" s="63"/>
-      <c r="P91" s="63"/>
-      <c r="Q91" s="63"/>
-      <c r="R91" s="63"/>
-      <c r="S91" s="63"/>
-      <c r="T91" s="63"/>
-      <c r="U91" s="64"/>
+      <c r="D91" s="75"/>
+      <c r="E91" s="51"/>
+      <c r="F91" s="51"/>
+      <c r="G91" s="51"/>
+      <c r="H91" s="51"/>
+      <c r="I91" s="51"/>
+      <c r="J91" s="51"/>
+      <c r="K91" s="51"/>
+      <c r="L91" s="51"/>
+      <c r="M91" s="51"/>
+      <c r="N91" s="51"/>
+      <c r="O91" s="51"/>
+      <c r="P91" s="51"/>
+      <c r="Q91" s="51"/>
+      <c r="R91" s="51"/>
+      <c r="S91" s="51"/>
+      <c r="T91" s="51"/>
+      <c r="U91" s="52"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="68"/>
@@ -5031,24 +5031,24 @@
       <c r="C92" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D92" s="83"/>
-      <c r="E92" s="63"/>
-      <c r="F92" s="63"/>
-      <c r="G92" s="63"/>
-      <c r="H92" s="63"/>
-      <c r="I92" s="63"/>
-      <c r="J92" s="63"/>
-      <c r="K92" s="63"/>
-      <c r="L92" s="63"/>
-      <c r="M92" s="63"/>
-      <c r="N92" s="63"/>
-      <c r="O92" s="63"/>
-      <c r="P92" s="63"/>
-      <c r="Q92" s="63"/>
-      <c r="R92" s="63"/>
-      <c r="S92" s="63"/>
-      <c r="T92" s="63"/>
-      <c r="U92" s="64"/>
+      <c r="D92" s="75"/>
+      <c r="E92" s="51"/>
+      <c r="F92" s="51"/>
+      <c r="G92" s="51"/>
+      <c r="H92" s="51"/>
+      <c r="I92" s="51"/>
+      <c r="J92" s="51"/>
+      <c r="K92" s="51"/>
+      <c r="L92" s="51"/>
+      <c r="M92" s="51"/>
+      <c r="N92" s="51"/>
+      <c r="O92" s="51"/>
+      <c r="P92" s="51"/>
+      <c r="Q92" s="51"/>
+      <c r="R92" s="51"/>
+      <c r="S92" s="51"/>
+      <c r="T92" s="51"/>
+      <c r="U92" s="52"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="68"/>
@@ -5058,24 +5058,24 @@
       <c r="C93" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D93" s="83"/>
-      <c r="E93" s="63"/>
-      <c r="F93" s="63"/>
-      <c r="G93" s="63"/>
-      <c r="H93" s="63"/>
-      <c r="I93" s="63"/>
-      <c r="J93" s="63"/>
-      <c r="K93" s="63"/>
-      <c r="L93" s="63"/>
-      <c r="M93" s="63"/>
-      <c r="N93" s="63"/>
-      <c r="O93" s="63"/>
-      <c r="P93" s="63"/>
-      <c r="Q93" s="63"/>
-      <c r="R93" s="63"/>
-      <c r="S93" s="63"/>
-      <c r="T93" s="63"/>
-      <c r="U93" s="64"/>
+      <c r="D93" s="75"/>
+      <c r="E93" s="51"/>
+      <c r="F93" s="51"/>
+      <c r="G93" s="51"/>
+      <c r="H93" s="51"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="51"/>
+      <c r="K93" s="51"/>
+      <c r="L93" s="51"/>
+      <c r="M93" s="51"/>
+      <c r="N93" s="51"/>
+      <c r="O93" s="51"/>
+      <c r="P93" s="51"/>
+      <c r="Q93" s="51"/>
+      <c r="R93" s="51"/>
+      <c r="S93" s="51"/>
+      <c r="T93" s="51"/>
+      <c r="U93" s="52"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A94" s="69"/>
@@ -5085,27 +5085,27 @@
       <c r="C94" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D94" s="84"/>
-      <c r="E94" s="65"/>
-      <c r="F94" s="65"/>
-      <c r="G94" s="65"/>
-      <c r="H94" s="65"/>
-      <c r="I94" s="65"/>
-      <c r="J94" s="65"/>
-      <c r="K94" s="65"/>
-      <c r="L94" s="65"/>
-      <c r="M94" s="65"/>
-      <c r="N94" s="65"/>
-      <c r="O94" s="65"/>
-      <c r="P94" s="65"/>
-      <c r="Q94" s="65"/>
-      <c r="R94" s="65"/>
-      <c r="S94" s="65"/>
-      <c r="T94" s="65"/>
-      <c r="U94" s="66"/>
+      <c r="D94" s="76"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53"/>
+      <c r="H94" s="53"/>
+      <c r="I94" s="53"/>
+      <c r="J94" s="53"/>
+      <c r="K94" s="53"/>
+      <c r="L94" s="53"/>
+      <c r="M94" s="53"/>
+      <c r="N94" s="53"/>
+      <c r="O94" s="53"/>
+      <c r="P94" s="53"/>
+      <c r="Q94" s="53"/>
+      <c r="R94" s="53"/>
+      <c r="S94" s="53"/>
+      <c r="T94" s="53"/>
+      <c r="U94" s="54"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="73">
+      <c r="A95" s="70">
         <v>14</v>
       </c>
       <c r="B95" s="28" t="s">
@@ -5138,7 +5138,7 @@
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="74"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="28" t="s">
         <v>138</v>
       </c>
@@ -5169,7 +5169,7 @@
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="74"/>
+      <c r="A97" s="71"/>
       <c r="B97" s="28" t="s">
         <v>139</v>
       </c>
@@ -5200,7 +5200,7 @@
       <c r="U97" s="17"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="74"/>
+      <c r="A98" s="71"/>
       <c r="B98" s="28" t="s">
         <v>140</v>
       </c>
@@ -5231,7 +5231,7 @@
       <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="74"/>
+      <c r="A99" s="71"/>
       <c r="B99" s="28" t="s">
         <v>141</v>
       </c>
@@ -5262,7 +5262,7 @@
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="74"/>
+      <c r="A100" s="71"/>
       <c r="B100" s="28" t="s">
         <v>142</v>
       </c>
@@ -5293,7 +5293,7 @@
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="75"/>
+      <c r="A101" s="72"/>
       <c r="B101" s="28" t="s">
         <v>143</v>
       </c>
@@ -5543,7 +5543,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="73">
+      <c r="A109" s="70">
         <v>16</v>
       </c>
       <c r="B109" s="28" t="s">
@@ -5576,7 +5576,7 @@
       <c r="U109" s="16"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="74"/>
+      <c r="A110" s="71"/>
       <c r="B110" s="28" t="s">
         <v>152</v>
       </c>
@@ -5607,7 +5607,7 @@
       <c r="U110" s="16"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="74"/>
+      <c r="A111" s="71"/>
       <c r="B111" s="28" t="s">
         <v>153</v>
       </c>
@@ -5638,7 +5638,7 @@
       <c r="U111" s="16"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="74"/>
+      <c r="A112" s="71"/>
       <c r="B112" s="28" t="s">
         <v>154</v>
       </c>
@@ -5669,7 +5669,7 @@
       <c r="U112" s="16"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="74"/>
+      <c r="A113" s="71"/>
       <c r="B113" s="28" t="s">
         <v>155</v>
       </c>
@@ -5700,7 +5700,7 @@
       <c r="U113" s="16"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="74"/>
+      <c r="A114" s="71"/>
       <c r="B114" s="28" t="s">
         <v>156</v>
       </c>
@@ -5731,7 +5731,7 @@
       <c r="U114" s="16"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="75"/>
+      <c r="A115" s="72"/>
       <c r="B115" s="28" t="s">
         <v>157</v>
       </c>
@@ -5981,7 +5981,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="73">
+      <c r="A123" s="70">
         <v>18</v>
       </c>
       <c r="B123" s="28" t="s">
@@ -6014,7 +6014,7 @@
       <c r="U123" s="16"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="74"/>
+      <c r="A124" s="71"/>
       <c r="B124" s="28" t="s">
         <v>166</v>
       </c>
@@ -6045,7 +6045,7 @@
       <c r="U124" s="16"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="74"/>
+      <c r="A125" s="71"/>
       <c r="B125" s="28" t="s">
         <v>167</v>
       </c>
@@ -6076,7 +6076,7 @@
       <c r="U125" s="16"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="74"/>
+      <c r="A126" s="71"/>
       <c r="B126" s="28" t="s">
         <v>168</v>
       </c>
@@ -6107,36 +6107,36 @@
       <c r="U126" s="16"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="74"/>
+      <c r="A127" s="71"/>
       <c r="B127" s="27" t="s">
         <v>169</v>
       </c>
       <c r="C127" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D127" s="81" t="s">
+      <c r="D127" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="E127" s="59"/>
-      <c r="F127" s="59"/>
-      <c r="G127" s="59"/>
-      <c r="H127" s="59"/>
-      <c r="I127" s="59"/>
-      <c r="J127" s="59"/>
-      <c r="K127" s="59"/>
-      <c r="L127" s="59"/>
-      <c r="M127" s="59"/>
-      <c r="N127" s="59"/>
-      <c r="O127" s="59"/>
-      <c r="P127" s="59"/>
-      <c r="Q127" s="59"/>
-      <c r="R127" s="59"/>
-      <c r="S127" s="59"/>
-      <c r="T127" s="59"/>
-      <c r="U127" s="60"/>
+      <c r="E127" s="47"/>
+      <c r="F127" s="47"/>
+      <c r="G127" s="47"/>
+      <c r="H127" s="47"/>
+      <c r="I127" s="47"/>
+      <c r="J127" s="47"/>
+      <c r="K127" s="47"/>
+      <c r="L127" s="47"/>
+      <c r="M127" s="47"/>
+      <c r="N127" s="47"/>
+      <c r="O127" s="47"/>
+      <c r="P127" s="47"/>
+      <c r="Q127" s="47"/>
+      <c r="R127" s="47"/>
+      <c r="S127" s="47"/>
+      <c r="T127" s="47"/>
+      <c r="U127" s="48"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="74"/>
+      <c r="A128" s="71"/>
       <c r="B128" s="28" t="s">
         <v>170</v>
       </c>
@@ -6167,7 +6167,7 @@
       <c r="U128" s="16"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="75"/>
+      <c r="A129" s="72"/>
       <c r="B129" s="28" t="s">
         <v>171</v>
       </c>
@@ -6432,17 +6432,16 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:U3"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
@@ -6459,16 +6458,17 @@
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="S2:U2"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6511,78 +6511,78 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="53" t="s">
+      <c r="C2" s="64"/>
+      <c r="D2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53" t="s">
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53" t="s">
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53" t="s">
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53" t="s">
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="54" t="s">
+      <c r="A3" s="55"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="53" t="s">
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53" t="s">
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53" t="s">
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53" t="s">
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="53"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53" t="s">
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="45">
@@ -6945,7 +6945,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="52">
+      <c r="A11" s="46">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -7011,7 +7011,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="52"/>
+      <c r="A12" s="46"/>
       <c r="B12" s="13" t="s">
         <v>47</v>
       </c>
@@ -7073,7 +7073,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="52"/>
+      <c r="A13" s="46"/>
       <c r="B13" s="13" t="s">
         <v>49</v>
       </c>
@@ -7125,7 +7125,7 @@
       <c r="AA13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="52"/>
+      <c r="A14" s="46"/>
       <c r="B14" s="13" t="s">
         <v>50</v>
       </c>
@@ -7189,7 +7189,7 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="52"/>
+      <c r="A15" s="46"/>
       <c r="B15" s="13" t="s">
         <v>54</v>
       </c>
@@ -7241,7 +7241,7 @@
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="52"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="13" t="s">
         <v>55</v>
       </c>
@@ -7273,7 +7273,7 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="52"/>
+      <c r="A17" s="46"/>
       <c r="B17" s="13" t="s">
         <v>56</v>
       </c>
@@ -7592,21 +7592,27 @@
       <c r="H24" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="43"/>
+      <c r="I24" s="43" t="s">
+        <v>180</v>
+      </c>
       <c r="J24" s="18" t="s">
         <v>33</v>
       </c>
       <c r="K24" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="L24" s="22"/>
+      <c r="L24" s="22" t="s">
+        <v>180</v>
+      </c>
       <c r="M24" s="18" t="s">
         <v>33</v>
       </c>
       <c r="N24" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="O24" s="22"/>
+      <c r="O24" s="22" t="s">
+        <v>180</v>
+      </c>
       <c r="P24" s="18"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="22"/>
@@ -7615,7 +7621,7 @@
       <c r="U24" s="22"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="52">
+      <c r="A25" s="46">
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -7646,7 +7652,7 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="52"/>
+      <c r="A26" s="46"/>
       <c r="B26" s="13" t="s">
         <v>65</v>
       </c>
@@ -7693,7 +7699,7 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="52"/>
+      <c r="A27" s="46"/>
       <c r="B27" s="13" t="s">
         <v>66</v>
       </c>
@@ -7740,7 +7746,7 @@
       <c r="U27" s="17"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="52"/>
+      <c r="A28" s="46"/>
       <c r="B28" s="13" t="s">
         <v>67</v>
       </c>
@@ -7787,87 +7793,87 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="52"/>
+      <c r="A29" s="46"/>
       <c r="B29" s="25" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
-      <c r="O29" s="46"/>
-      <c r="P29" s="46"/>
-      <c r="Q29" s="46"/>
-      <c r="R29" s="46"/>
-      <c r="S29" s="46"/>
-      <c r="T29" s="46"/>
-      <c r="U29" s="47"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="56"/>
+      <c r="R29" s="56"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="56"/>
+      <c r="U29" s="57"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="52"/>
+      <c r="A30" s="46"/>
       <c r="B30" s="25" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="48"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="49"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="58"/>
+      <c r="R30" s="58"/>
+      <c r="S30" s="58"/>
+      <c r="T30" s="58"/>
+      <c r="U30" s="59"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="52"/>
+      <c r="A31" s="46"/>
       <c r="B31" s="25" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="51"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="45">
@@ -8002,26 +8008,26 @@
       <c r="C35" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="46" t="s">
+      <c r="D35" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="46"/>
-      <c r="P35" s="46"/>
-      <c r="Q35" s="46"/>
-      <c r="R35" s="46"/>
-      <c r="S35" s="46"/>
-      <c r="T35" s="46"/>
-      <c r="U35" s="47"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="56"/>
+      <c r="O35" s="56"/>
+      <c r="P35" s="56"/>
+      <c r="Q35" s="56"/>
+      <c r="R35" s="56"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="56"/>
+      <c r="U35" s="57"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A36" s="45"/>
@@ -8031,24 +8037,24 @@
       <c r="C36" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="48"/>
-      <c r="N36" s="48"/>
-      <c r="O36" s="48"/>
-      <c r="P36" s="48"/>
-      <c r="Q36" s="48"/>
-      <c r="R36" s="48"/>
-      <c r="S36" s="48"/>
-      <c r="T36" s="48"/>
-      <c r="U36" s="49"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="58"/>
+      <c r="L36" s="58"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="58"/>
+      <c r="O36" s="58"/>
+      <c r="P36" s="58"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="58"/>
+      <c r="S36" s="58"/>
+      <c r="T36" s="58"/>
+      <c r="U36" s="59"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="45"/>
@@ -8058,24 +8064,24 @@
       <c r="C37" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
-      <c r="L37" s="48"/>
-      <c r="M37" s="48"/>
-      <c r="N37" s="48"/>
-      <c r="O37" s="48"/>
-      <c r="P37" s="48"/>
-      <c r="Q37" s="48"/>
-      <c r="R37" s="48"/>
-      <c r="S37" s="48"/>
-      <c r="T37" s="48"/>
-      <c r="U37" s="49"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="58"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="58"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="58"/>
+      <c r="Q37" s="58"/>
+      <c r="R37" s="58"/>
+      <c r="S37" s="58"/>
+      <c r="T37" s="58"/>
+      <c r="U37" s="59"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A38" s="45"/>
@@ -8085,27 +8091,27 @@
       <c r="C38" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="48"/>
-      <c r="L38" s="48"/>
-      <c r="M38" s="48"/>
-      <c r="N38" s="48"/>
-      <c r="O38" s="48"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="48"/>
-      <c r="R38" s="48"/>
-      <c r="S38" s="48"/>
-      <c r="T38" s="48"/>
-      <c r="U38" s="49"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="58"/>
+      <c r="S38" s="58"/>
+      <c r="T38" s="58"/>
+      <c r="U38" s="59"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="52">
+      <c r="A39" s="46">
         <v>6</v>
       </c>
       <c r="B39" s="27" t="s">
@@ -8114,81 +8120,81 @@
       <c r="C39" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
-      <c r="L39" s="48"/>
-      <c r="M39" s="48"/>
-      <c r="N39" s="48"/>
-      <c r="O39" s="48"/>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="48"/>
-      <c r="R39" s="48"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="48"/>
-      <c r="U39" s="49"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="58"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
+      <c r="P39" s="58"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="58"/>
+      <c r="S39" s="58"/>
+      <c r="T39" s="58"/>
+      <c r="U39" s="59"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="52"/>
+      <c r="A40" s="46"/>
       <c r="B40" s="27" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
-      <c r="L40" s="48"/>
-      <c r="M40" s="48"/>
-      <c r="N40" s="48"/>
-      <c r="O40" s="48"/>
-      <c r="P40" s="48"/>
-      <c r="Q40" s="48"/>
-      <c r="R40" s="48"/>
-      <c r="S40" s="48"/>
-      <c r="T40" s="48"/>
-      <c r="U40" s="49"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="58"/>
+      <c r="Q40" s="58"/>
+      <c r="R40" s="58"/>
+      <c r="S40" s="58"/>
+      <c r="T40" s="58"/>
+      <c r="U40" s="59"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="52"/>
+      <c r="A41" s="46"/>
       <c r="B41" s="27" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
-      <c r="O41" s="50"/>
-      <c r="P41" s="50"/>
-      <c r="Q41" s="50"/>
-      <c r="R41" s="50"/>
-      <c r="S41" s="50"/>
-      <c r="T41" s="50"/>
-      <c r="U41" s="51"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="61"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="52"/>
+      <c r="A42" s="46"/>
       <c r="B42" s="28" t="s">
         <v>82</v>
       </c>
@@ -8247,7 +8253,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="52"/>
+      <c r="A43" s="46"/>
       <c r="B43" s="28" t="s">
         <v>83</v>
       </c>
@@ -8294,7 +8300,7 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="52"/>
+      <c r="A44" s="46"/>
       <c r="B44" s="29" t="s">
         <v>84</v>
       </c>
@@ -8321,7 +8327,7 @@
       <c r="U44" s="22"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="52"/>
+      <c r="A45" s="46"/>
       <c r="B45" s="28" t="s">
         <v>85</v>
       </c>
@@ -8632,7 +8638,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="52">
+      <c r="A53" s="46">
         <v>8</v>
       </c>
       <c r="B53" s="28" t="s">
@@ -8681,7 +8687,7 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="52"/>
+      <c r="A54" s="46"/>
       <c r="B54" s="28" t="s">
         <v>94</v>
       </c>
@@ -8728,7 +8734,7 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="52"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="28" t="s">
         <v>95</v>
       </c>
@@ -8775,7 +8781,7 @@
       <c r="U55" s="17"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="52"/>
+      <c r="A56" s="46"/>
       <c r="B56" s="28" t="s">
         <v>96</v>
       </c>
@@ -8834,7 +8840,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="52"/>
+      <c r="A57" s="46"/>
       <c r="B57" s="28" t="s">
         <v>97</v>
       </c>
@@ -8881,7 +8887,7 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="52"/>
+      <c r="A58" s="46"/>
       <c r="B58" s="28" t="s">
         <v>98</v>
       </c>
@@ -8908,7 +8914,7 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="52"/>
+      <c r="A59" s="46"/>
       <c r="B59" s="28" t="s">
         <v>99</v>
       </c>
@@ -9202,7 +9208,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="52">
+      <c r="A67" s="46">
         <v>10</v>
       </c>
       <c r="B67" s="28" t="s">
@@ -9233,7 +9239,7 @@
       <c r="U67" s="16"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="52"/>
+      <c r="A68" s="46"/>
       <c r="B68" s="28" t="s">
         <v>108</v>
       </c>
@@ -9280,7 +9286,7 @@
       <c r="U68" s="16"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="52"/>
+      <c r="A69" s="46"/>
       <c r="B69" s="28" t="s">
         <v>109</v>
       </c>
@@ -9309,7 +9315,7 @@
       <c r="U69" s="16"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="52"/>
+      <c r="A70" s="46"/>
       <c r="B70" s="28" t="s">
         <v>110</v>
       </c>
@@ -9350,7 +9356,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="52"/>
+      <c r="A71" s="46"/>
       <c r="B71" s="28" t="s">
         <v>111</v>
       </c>
@@ -9397,7 +9403,7 @@
       <c r="U71" s="16"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="52"/>
+      <c r="A72" s="46"/>
       <c r="B72" s="28" t="s">
         <v>112</v>
       </c>
@@ -9424,7 +9430,7 @@
       <c r="U72" s="16"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="52"/>
+      <c r="A73" s="46"/>
       <c r="B73" s="28" t="s">
         <v>113</v>
       </c>
@@ -9688,7 +9694,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="52">
+      <c r="A81" s="46">
         <v>12</v>
       </c>
       <c r="B81" s="28" t="s">
@@ -9697,188 +9703,188 @@
       <c r="C81" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="61" t="s">
+      <c r="D81" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="E81" s="61"/>
-      <c r="F81" s="61"/>
-      <c r="G81" s="61"/>
-      <c r="H81" s="61"/>
-      <c r="I81" s="61"/>
-      <c r="J81" s="61"/>
-      <c r="K81" s="61"/>
-      <c r="L81" s="61"/>
-      <c r="M81" s="61"/>
-      <c r="N81" s="61"/>
-      <c r="O81" s="61"/>
-      <c r="P81" s="61"/>
-      <c r="Q81" s="61"/>
-      <c r="R81" s="61"/>
-      <c r="S81" s="61"/>
-      <c r="T81" s="61"/>
-      <c r="U81" s="62"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="49"/>
+      <c r="H81" s="49"/>
+      <c r="I81" s="49"/>
+      <c r="J81" s="49"/>
+      <c r="K81" s="49"/>
+      <c r="L81" s="49"/>
+      <c r="M81" s="49"/>
+      <c r="N81" s="49"/>
+      <c r="O81" s="49"/>
+      <c r="P81" s="49"/>
+      <c r="Q81" s="49"/>
+      <c r="R81" s="49"/>
+      <c r="S81" s="49"/>
+      <c r="T81" s="49"/>
+      <c r="U81" s="50"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="52"/>
+      <c r="A82" s="46"/>
       <c r="B82" s="28" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="63"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="63"/>
-      <c r="G82" s="63"/>
-      <c r="H82" s="63"/>
-      <c r="I82" s="63"/>
-      <c r="J82" s="63"/>
-      <c r="K82" s="63"/>
-      <c r="L82" s="63"/>
-      <c r="M82" s="63"/>
-      <c r="N82" s="63"/>
-      <c r="O82" s="63"/>
-      <c r="P82" s="63"/>
-      <c r="Q82" s="63"/>
-      <c r="R82" s="63"/>
-      <c r="S82" s="63"/>
-      <c r="T82" s="63"/>
-      <c r="U82" s="64"/>
+      <c r="D82" s="51"/>
+      <c r="E82" s="51"/>
+      <c r="F82" s="51"/>
+      <c r="G82" s="51"/>
+      <c r="H82" s="51"/>
+      <c r="I82" s="51"/>
+      <c r="J82" s="51"/>
+      <c r="K82" s="51"/>
+      <c r="L82" s="51"/>
+      <c r="M82" s="51"/>
+      <c r="N82" s="51"/>
+      <c r="O82" s="51"/>
+      <c r="P82" s="51"/>
+      <c r="Q82" s="51"/>
+      <c r="R82" s="51"/>
+      <c r="S82" s="51"/>
+      <c r="T82" s="51"/>
+      <c r="U82" s="52"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="52"/>
+      <c r="A83" s="46"/>
       <c r="B83" s="28" t="s">
         <v>124</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D83" s="63"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="63"/>
-      <c r="I83" s="63"/>
-      <c r="J83" s="63"/>
-      <c r="K83" s="63"/>
-      <c r="L83" s="63"/>
-      <c r="M83" s="63"/>
-      <c r="N83" s="63"/>
-      <c r="O83" s="63"/>
-      <c r="P83" s="63"/>
-      <c r="Q83" s="63"/>
-      <c r="R83" s="63"/>
-      <c r="S83" s="63"/>
-      <c r="T83" s="63"/>
-      <c r="U83" s="64"/>
+      <c r="D83" s="51"/>
+      <c r="E83" s="51"/>
+      <c r="F83" s="51"/>
+      <c r="G83" s="51"/>
+      <c r="H83" s="51"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="51"/>
+      <c r="K83" s="51"/>
+      <c r="L83" s="51"/>
+      <c r="M83" s="51"/>
+      <c r="N83" s="51"/>
+      <c r="O83" s="51"/>
+      <c r="P83" s="51"/>
+      <c r="Q83" s="51"/>
+      <c r="R83" s="51"/>
+      <c r="S83" s="51"/>
+      <c r="T83" s="51"/>
+      <c r="U83" s="52"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="52"/>
+      <c r="A84" s="46"/>
       <c r="B84" s="28" t="s">
         <v>125</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D84" s="63"/>
-      <c r="E84" s="63"/>
-      <c r="F84" s="63"/>
-      <c r="G84" s="63"/>
-      <c r="H84" s="63"/>
-      <c r="I84" s="63"/>
-      <c r="J84" s="63"/>
-      <c r="K84" s="63"/>
-      <c r="L84" s="63"/>
-      <c r="M84" s="63"/>
-      <c r="N84" s="63"/>
-      <c r="O84" s="63"/>
-      <c r="P84" s="63"/>
-      <c r="Q84" s="63"/>
-      <c r="R84" s="63"/>
-      <c r="S84" s="63"/>
-      <c r="T84" s="63"/>
-      <c r="U84" s="64"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="51"/>
+      <c r="I84" s="51"/>
+      <c r="J84" s="51"/>
+      <c r="K84" s="51"/>
+      <c r="L84" s="51"/>
+      <c r="M84" s="51"/>
+      <c r="N84" s="51"/>
+      <c r="O84" s="51"/>
+      <c r="P84" s="51"/>
+      <c r="Q84" s="51"/>
+      <c r="R84" s="51"/>
+      <c r="S84" s="51"/>
+      <c r="T84" s="51"/>
+      <c r="U84" s="52"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="52"/>
+      <c r="A85" s="46"/>
       <c r="B85" s="28" t="s">
         <v>126</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D85" s="63"/>
-      <c r="E85" s="63"/>
-      <c r="F85" s="63"/>
-      <c r="G85" s="63"/>
-      <c r="H85" s="63"/>
-      <c r="I85" s="63"/>
-      <c r="J85" s="63"/>
-      <c r="K85" s="63"/>
-      <c r="L85" s="63"/>
-      <c r="M85" s="63"/>
-      <c r="N85" s="63"/>
-      <c r="O85" s="63"/>
-      <c r="P85" s="63"/>
-      <c r="Q85" s="63"/>
-      <c r="R85" s="63"/>
-      <c r="S85" s="63"/>
-      <c r="T85" s="63"/>
-      <c r="U85" s="64"/>
+      <c r="D85" s="51"/>
+      <c r="E85" s="51"/>
+      <c r="F85" s="51"/>
+      <c r="G85" s="51"/>
+      <c r="H85" s="51"/>
+      <c r="I85" s="51"/>
+      <c r="J85" s="51"/>
+      <c r="K85" s="51"/>
+      <c r="L85" s="51"/>
+      <c r="M85" s="51"/>
+      <c r="N85" s="51"/>
+      <c r="O85" s="51"/>
+      <c r="P85" s="51"/>
+      <c r="Q85" s="51"/>
+      <c r="R85" s="51"/>
+      <c r="S85" s="51"/>
+      <c r="T85" s="51"/>
+      <c r="U85" s="52"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="52"/>
+      <c r="A86" s="46"/>
       <c r="B86" s="28" t="s">
         <v>127</v>
       </c>
       <c r="C86" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="63"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="63"/>
-      <c r="G86" s="63"/>
-      <c r="H86" s="63"/>
-      <c r="I86" s="63"/>
-      <c r="J86" s="63"/>
-      <c r="K86" s="63"/>
-      <c r="L86" s="63"/>
-      <c r="M86" s="63"/>
-      <c r="N86" s="63"/>
-      <c r="O86" s="63"/>
-      <c r="P86" s="63"/>
-      <c r="Q86" s="63"/>
-      <c r="R86" s="63"/>
-      <c r="S86" s="63"/>
-      <c r="T86" s="63"/>
-      <c r="U86" s="64"/>
+      <c r="D86" s="51"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="51"/>
+      <c r="G86" s="51"/>
+      <c r="H86" s="51"/>
+      <c r="I86" s="51"/>
+      <c r="J86" s="51"/>
+      <c r="K86" s="51"/>
+      <c r="L86" s="51"/>
+      <c r="M86" s="51"/>
+      <c r="N86" s="51"/>
+      <c r="O86" s="51"/>
+      <c r="P86" s="51"/>
+      <c r="Q86" s="51"/>
+      <c r="R86" s="51"/>
+      <c r="S86" s="51"/>
+      <c r="T86" s="51"/>
+      <c r="U86" s="52"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="52"/>
+      <c r="A87" s="46"/>
       <c r="B87" s="28" t="s">
         <v>128</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D87" s="63"/>
-      <c r="E87" s="63"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="63"/>
-      <c r="H87" s="63"/>
-      <c r="I87" s="63"/>
-      <c r="J87" s="63"/>
-      <c r="K87" s="63"/>
-      <c r="L87" s="63"/>
-      <c r="M87" s="63"/>
-      <c r="N87" s="63"/>
-      <c r="O87" s="63"/>
-      <c r="P87" s="63"/>
-      <c r="Q87" s="63"/>
-      <c r="R87" s="63"/>
-      <c r="S87" s="63"/>
-      <c r="T87" s="63"/>
-      <c r="U87" s="64"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="51"/>
+      <c r="J87" s="51"/>
+      <c r="K87" s="51"/>
+      <c r="L87" s="51"/>
+      <c r="M87" s="51"/>
+      <c r="N87" s="51"/>
+      <c r="O87" s="51"/>
+      <c r="P87" s="51"/>
+      <c r="Q87" s="51"/>
+      <c r="R87" s="51"/>
+      <c r="S87" s="51"/>
+      <c r="T87" s="51"/>
+      <c r="U87" s="52"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A88" s="45">
@@ -9890,24 +9896,24 @@
       <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="63"/>
-      <c r="E88" s="63"/>
-      <c r="F88" s="63"/>
-      <c r="G88" s="63"/>
-      <c r="H88" s="63"/>
-      <c r="I88" s="63"/>
-      <c r="J88" s="63"/>
-      <c r="K88" s="63"/>
-      <c r="L88" s="63"/>
-      <c r="M88" s="63"/>
-      <c r="N88" s="63"/>
-      <c r="O88" s="63"/>
-      <c r="P88" s="63"/>
-      <c r="Q88" s="63"/>
-      <c r="R88" s="63"/>
-      <c r="S88" s="63"/>
-      <c r="T88" s="63"/>
-      <c r="U88" s="64"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="51"/>
+      <c r="J88" s="51"/>
+      <c r="K88" s="51"/>
+      <c r="L88" s="51"/>
+      <c r="M88" s="51"/>
+      <c r="N88" s="51"/>
+      <c r="O88" s="51"/>
+      <c r="P88" s="51"/>
+      <c r="Q88" s="51"/>
+      <c r="R88" s="51"/>
+      <c r="S88" s="51"/>
+      <c r="T88" s="51"/>
+      <c r="U88" s="52"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A89" s="45"/>
@@ -9917,24 +9923,24 @@
       <c r="C89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="63"/>
-      <c r="E89" s="63"/>
-      <c r="F89" s="63"/>
-      <c r="G89" s="63"/>
-      <c r="H89" s="63"/>
-      <c r="I89" s="63"/>
-      <c r="J89" s="63"/>
-      <c r="K89" s="63"/>
-      <c r="L89" s="63"/>
-      <c r="M89" s="63"/>
-      <c r="N89" s="63"/>
-      <c r="O89" s="63"/>
-      <c r="P89" s="63"/>
-      <c r="Q89" s="63"/>
-      <c r="R89" s="63"/>
-      <c r="S89" s="63"/>
-      <c r="T89" s="63"/>
-      <c r="U89" s="64"/>
+      <c r="D89" s="51"/>
+      <c r="E89" s="51"/>
+      <c r="F89" s="51"/>
+      <c r="G89" s="51"/>
+      <c r="H89" s="51"/>
+      <c r="I89" s="51"/>
+      <c r="J89" s="51"/>
+      <c r="K89" s="51"/>
+      <c r="L89" s="51"/>
+      <c r="M89" s="51"/>
+      <c r="N89" s="51"/>
+      <c r="O89" s="51"/>
+      <c r="P89" s="51"/>
+      <c r="Q89" s="51"/>
+      <c r="R89" s="51"/>
+      <c r="S89" s="51"/>
+      <c r="T89" s="51"/>
+      <c r="U89" s="52"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A90" s="45"/>
@@ -9944,24 +9950,24 @@
       <c r="C90" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D90" s="63"/>
-      <c r="E90" s="63"/>
-      <c r="F90" s="63"/>
-      <c r="G90" s="63"/>
-      <c r="H90" s="63"/>
-      <c r="I90" s="63"/>
-      <c r="J90" s="63"/>
-      <c r="K90" s="63"/>
-      <c r="L90" s="63"/>
-      <c r="M90" s="63"/>
-      <c r="N90" s="63"/>
-      <c r="O90" s="63"/>
-      <c r="P90" s="63"/>
-      <c r="Q90" s="63"/>
-      <c r="R90" s="63"/>
-      <c r="S90" s="63"/>
-      <c r="T90" s="63"/>
-      <c r="U90" s="64"/>
+      <c r="D90" s="51"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="51"/>
+      <c r="G90" s="51"/>
+      <c r="H90" s="51"/>
+      <c r="I90" s="51"/>
+      <c r="J90" s="51"/>
+      <c r="K90" s="51"/>
+      <c r="L90" s="51"/>
+      <c r="M90" s="51"/>
+      <c r="N90" s="51"/>
+      <c r="O90" s="51"/>
+      <c r="P90" s="51"/>
+      <c r="Q90" s="51"/>
+      <c r="R90" s="51"/>
+      <c r="S90" s="51"/>
+      <c r="T90" s="51"/>
+      <c r="U90" s="52"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="45"/>
@@ -9971,24 +9977,24 @@
       <c r="C91" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D91" s="63"/>
-      <c r="E91" s="63"/>
-      <c r="F91" s="63"/>
-      <c r="G91" s="63"/>
-      <c r="H91" s="63"/>
-      <c r="I91" s="63"/>
-      <c r="J91" s="63"/>
-      <c r="K91" s="63"/>
-      <c r="L91" s="63"/>
-      <c r="M91" s="63"/>
-      <c r="N91" s="63"/>
-      <c r="O91" s="63"/>
-      <c r="P91" s="63"/>
-      <c r="Q91" s="63"/>
-      <c r="R91" s="63"/>
-      <c r="S91" s="63"/>
-      <c r="T91" s="63"/>
-      <c r="U91" s="64"/>
+      <c r="D91" s="51"/>
+      <c r="E91" s="51"/>
+      <c r="F91" s="51"/>
+      <c r="G91" s="51"/>
+      <c r="H91" s="51"/>
+      <c r="I91" s="51"/>
+      <c r="J91" s="51"/>
+      <c r="K91" s="51"/>
+      <c r="L91" s="51"/>
+      <c r="M91" s="51"/>
+      <c r="N91" s="51"/>
+      <c r="O91" s="51"/>
+      <c r="P91" s="51"/>
+      <c r="Q91" s="51"/>
+      <c r="R91" s="51"/>
+      <c r="S91" s="51"/>
+      <c r="T91" s="51"/>
+      <c r="U91" s="52"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="45"/>
@@ -9998,24 +10004,24 @@
       <c r="C92" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D92" s="63"/>
-      <c r="E92" s="63"/>
-      <c r="F92" s="63"/>
-      <c r="G92" s="63"/>
-      <c r="H92" s="63"/>
-      <c r="I92" s="63"/>
-      <c r="J92" s="63"/>
-      <c r="K92" s="63"/>
-      <c r="L92" s="63"/>
-      <c r="M92" s="63"/>
-      <c r="N92" s="63"/>
-      <c r="O92" s="63"/>
-      <c r="P92" s="63"/>
-      <c r="Q92" s="63"/>
-      <c r="R92" s="63"/>
-      <c r="S92" s="63"/>
-      <c r="T92" s="63"/>
-      <c r="U92" s="64"/>
+      <c r="D92" s="51"/>
+      <c r="E92" s="51"/>
+      <c r="F92" s="51"/>
+      <c r="G92" s="51"/>
+      <c r="H92" s="51"/>
+      <c r="I92" s="51"/>
+      <c r="J92" s="51"/>
+      <c r="K92" s="51"/>
+      <c r="L92" s="51"/>
+      <c r="M92" s="51"/>
+      <c r="N92" s="51"/>
+      <c r="O92" s="51"/>
+      <c r="P92" s="51"/>
+      <c r="Q92" s="51"/>
+      <c r="R92" s="51"/>
+      <c r="S92" s="51"/>
+      <c r="T92" s="51"/>
+      <c r="U92" s="52"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="45"/>
@@ -10025,24 +10031,24 @@
       <c r="C93" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D93" s="63"/>
-      <c r="E93" s="63"/>
-      <c r="F93" s="63"/>
-      <c r="G93" s="63"/>
-      <c r="H93" s="63"/>
-      <c r="I93" s="63"/>
-      <c r="J93" s="63"/>
-      <c r="K93" s="63"/>
-      <c r="L93" s="63"/>
-      <c r="M93" s="63"/>
-      <c r="N93" s="63"/>
-      <c r="O93" s="63"/>
-      <c r="P93" s="63"/>
-      <c r="Q93" s="63"/>
-      <c r="R93" s="63"/>
-      <c r="S93" s="63"/>
-      <c r="T93" s="63"/>
-      <c r="U93" s="64"/>
+      <c r="D93" s="51"/>
+      <c r="E93" s="51"/>
+      <c r="F93" s="51"/>
+      <c r="G93" s="51"/>
+      <c r="H93" s="51"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="51"/>
+      <c r="K93" s="51"/>
+      <c r="L93" s="51"/>
+      <c r="M93" s="51"/>
+      <c r="N93" s="51"/>
+      <c r="O93" s="51"/>
+      <c r="P93" s="51"/>
+      <c r="Q93" s="51"/>
+      <c r="R93" s="51"/>
+      <c r="S93" s="51"/>
+      <c r="T93" s="51"/>
+      <c r="U93" s="52"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A94" s="45"/>
@@ -10052,27 +10058,27 @@
       <c r="C94" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D94" s="65"/>
-      <c r="E94" s="65"/>
-      <c r="F94" s="65"/>
-      <c r="G94" s="65"/>
-      <c r="H94" s="65"/>
-      <c r="I94" s="65"/>
-      <c r="J94" s="65"/>
-      <c r="K94" s="65"/>
-      <c r="L94" s="65"/>
-      <c r="M94" s="65"/>
-      <c r="N94" s="65"/>
-      <c r="O94" s="65"/>
-      <c r="P94" s="65"/>
-      <c r="Q94" s="65"/>
-      <c r="R94" s="65"/>
-      <c r="S94" s="65"/>
-      <c r="T94" s="65"/>
-      <c r="U94" s="66"/>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53"/>
+      <c r="H94" s="53"/>
+      <c r="I94" s="53"/>
+      <c r="J94" s="53"/>
+      <c r="K94" s="53"/>
+      <c r="L94" s="53"/>
+      <c r="M94" s="53"/>
+      <c r="N94" s="53"/>
+      <c r="O94" s="53"/>
+      <c r="P94" s="53"/>
+      <c r="Q94" s="53"/>
+      <c r="R94" s="53"/>
+      <c r="S94" s="53"/>
+      <c r="T94" s="53"/>
+      <c r="U94" s="54"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="52">
+      <c r="A95" s="46">
         <v>14</v>
       </c>
       <c r="B95" s="28" t="s">
@@ -10105,7 +10111,7 @@
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="52"/>
+      <c r="A96" s="46"/>
       <c r="B96" s="28" t="s">
         <v>138</v>
       </c>
@@ -10136,7 +10142,7 @@
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="52"/>
+      <c r="A97" s="46"/>
       <c r="B97" s="28" t="s">
         <v>139</v>
       </c>
@@ -10167,7 +10173,7 @@
       <c r="U97" s="17"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="52"/>
+      <c r="A98" s="46"/>
       <c r="B98" s="28" t="s">
         <v>140</v>
       </c>
@@ -10198,7 +10204,7 @@
       <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="52"/>
+      <c r="A99" s="46"/>
       <c r="B99" s="28" t="s">
         <v>141</v>
       </c>
@@ -10229,7 +10235,7 @@
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="52"/>
+      <c r="A100" s="46"/>
       <c r="B100" s="28" t="s">
         <v>142</v>
       </c>
@@ -10260,7 +10266,7 @@
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="52"/>
+      <c r="A101" s="46"/>
       <c r="B101" s="28" t="s">
         <v>143</v>
       </c>
@@ -10510,7 +10516,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="52">
+      <c r="A109" s="46">
         <v>16</v>
       </c>
       <c r="B109" s="28" t="s">
@@ -10543,7 +10549,7 @@
       <c r="U109" s="16"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="52"/>
+      <c r="A110" s="46"/>
       <c r="B110" s="28" t="s">
         <v>152</v>
       </c>
@@ -10574,7 +10580,7 @@
       <c r="U110" s="16"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="52"/>
+      <c r="A111" s="46"/>
       <c r="B111" s="28" t="s">
         <v>153</v>
       </c>
@@ -10605,7 +10611,7 @@
       <c r="U111" s="16"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="52"/>
+      <c r="A112" s="46"/>
       <c r="B112" s="28" t="s">
         <v>154</v>
       </c>
@@ -10636,7 +10642,7 @@
       <c r="U112" s="16"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="52"/>
+      <c r="A113" s="46"/>
       <c r="B113" s="28" t="s">
         <v>155</v>
       </c>
@@ -10667,7 +10673,7 @@
       <c r="U113" s="16"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="52"/>
+      <c r="A114" s="46"/>
       <c r="B114" s="28" t="s">
         <v>156</v>
       </c>
@@ -10698,7 +10704,7 @@
       <c r="U114" s="16"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="52"/>
+      <c r="A115" s="46"/>
       <c r="B115" s="28" t="s">
         <v>157</v>
       </c>
@@ -10948,7 +10954,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="52">
+      <c r="A123" s="46">
         <v>18</v>
       </c>
       <c r="B123" s="28" t="s">
@@ -10981,7 +10987,7 @@
       <c r="U123" s="16"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="52"/>
+      <c r="A124" s="46"/>
       <c r="B124" s="28" t="s">
         <v>166</v>
       </c>
@@ -11012,7 +11018,7 @@
       <c r="U124" s="16"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="52"/>
+      <c r="A125" s="46"/>
       <c r="B125" s="28" t="s">
         <v>167</v>
       </c>
@@ -11043,7 +11049,7 @@
       <c r="U125" s="16"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="52"/>
+      <c r="A126" s="46"/>
       <c r="B126" s="28" t="s">
         <v>168</v>
       </c>
@@ -11074,36 +11080,36 @@
       <c r="U126" s="16"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="52"/>
+      <c r="A127" s="46"/>
       <c r="B127" s="27" t="s">
         <v>169</v>
       </c>
       <c r="C127" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D127" s="59" t="s">
+      <c r="D127" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="E127" s="59"/>
-      <c r="F127" s="59"/>
-      <c r="G127" s="59"/>
-      <c r="H127" s="59"/>
-      <c r="I127" s="59"/>
-      <c r="J127" s="59"/>
-      <c r="K127" s="59"/>
-      <c r="L127" s="59"/>
-      <c r="M127" s="59"/>
-      <c r="N127" s="59"/>
-      <c r="O127" s="59"/>
-      <c r="P127" s="59"/>
-      <c r="Q127" s="59"/>
-      <c r="R127" s="59"/>
-      <c r="S127" s="59"/>
-      <c r="T127" s="59"/>
-      <c r="U127" s="60"/>
+      <c r="E127" s="47"/>
+      <c r="F127" s="47"/>
+      <c r="G127" s="47"/>
+      <c r="H127" s="47"/>
+      <c r="I127" s="47"/>
+      <c r="J127" s="47"/>
+      <c r="K127" s="47"/>
+      <c r="L127" s="47"/>
+      <c r="M127" s="47"/>
+      <c r="N127" s="47"/>
+      <c r="O127" s="47"/>
+      <c r="P127" s="47"/>
+      <c r="Q127" s="47"/>
+      <c r="R127" s="47"/>
+      <c r="S127" s="47"/>
+      <c r="T127" s="47"/>
+      <c r="U127" s="48"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="52"/>
+      <c r="A128" s="46"/>
       <c r="B128" s="28" t="s">
         <v>170</v>
       </c>
@@ -11134,7 +11140,7 @@
       <c r="U128" s="16"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="52"/>
+      <c r="A129" s="46"/>
       <c r="B129" s="28" t="s">
         <v>171</v>
       </c>
@@ -11399,17 +11405,16 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:U3"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
@@ -11426,16 +11431,17 @@
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="S2:U2"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
